--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -139,6 +139,9 @@
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2306,10 +2309,10 @@
       </c>
     </row>
     <row r="60"/>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>STEP 2 — which family owns the variation</t>
+    <row r="61" ht="84" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it</t>
         </is>
       </c>
       <c r="B61" s="7" t="n"/>
@@ -2364,22 +2367,22 @@
           <t>Between sites</t>
         </is>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="19">
         <f>12*SUMSQ(E56:E57)</f>
         <v/>
       </c>
       <c r="C63" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="19">
         <f>B63/C63</f>
         <v/>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="19">
         <f>MAX(0,(D63-D64)/12)</f>
         <v/>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="20">
         <f>IFERROR(E63/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2395,22 +2398,22 @@
           <t>Between teams, within a site</t>
         </is>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="19">
         <f>6*SUMSQ(E52:E55)</f>
         <v/>
       </c>
       <c r="C64" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="18">
+      <c r="D64" s="19">
         <f>B64/C64</f>
         <v/>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="19">
         <f>MAX(0,(D64-D65)/6)</f>
         <v/>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="20">
         <f>IFERROR(E64/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2426,22 +2429,22 @@
           <t>Between agents, within a team</t>
         </is>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="19">
         <f>2*SUMSQ(E40:E51)</f>
         <v/>
       </c>
       <c r="C65" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D65" s="18">
+      <c r="D65" s="19">
         <f>B65/C65</f>
         <v/>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="19">
         <f>MAX(0,(D65-D66)/2)</f>
         <v/>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="20">
         <f>IFERROR(E65/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2457,22 +2460,22 @@
           <t>Within one agent, contact to contact</t>
         </is>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="19">
         <f>SUMSQ(F40:F51)/2</f>
         <v/>
       </c>
       <c r="C66" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="D66" s="18">
+      <c r="D66" s="19">
         <f>B66/C66</f>
         <v/>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="19">
         <f>D66</f>
         <v/>
       </c>
-      <c r="F66" s="19">
+      <c r="F66" s="20">
         <f>IFERROR(E66/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2488,14 +2491,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="19">
         <f>DEVSQ(E12:E35)</f>
         <v/>
       </c>
       <c r="C67" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f>IFERROR(SUM(F63:F66),"")</f>
         <v/>
       </c>
@@ -2540,7 +2543,7 @@
           <t>Look here first</t>
         </is>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="21">
         <f>IFERROR(INDEX($A$63:$A$66,MATCH(MAX($F$63:$F$66),$F$63:$F$66,0)),"")</f>
         <v/>
       </c>
@@ -2572,7 +2575,7 @@
           <t>Is that gap worth chasing?</t>
         </is>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="21">
         <f>IF(B73="","",IF(B73&gt;=$B$8,"YES — larger than the difference you said would matter","NO — smaller than the difference you said would matter"))</f>
         <v/>
       </c>

--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -2309,10 +2309,10 @@
       </c>
     </row>
     <row r="60"/>
-    <row r="61" ht="84" customHeight="1">
+    <row r="61" ht="132" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it</t>
+          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it · Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
         </is>
       </c>
       <c r="B61" s="7" t="n"/>

--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -2309,10 +2309,10 @@
       </c>
     </row>
     <row r="60"/>
-    <row r="61" ht="132" customHeight="1">
+    <row r="61" ht="168" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it · Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
+          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64). It is what a sum of squares is divided by to get a mean square, and it is why a family measured across two levels can never be pinned down as tightly as one measured across ten · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it · Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
         </is>
       </c>
       <c r="B61" s="7" t="n"/>

--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -2309,10 +2309,14 @@
       </c>
     </row>
     <row r="60"/>
-    <row r="61" ht="168" customHeight="1">
+    <row r="61" ht="204" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>STEP 2 — which family owns the variation  ·  Key: Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared · Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64). It is what a sum of squares is divided by to get a mean square, and it is why a family measured across two levels can never be pinned down as tightly as one measured across ten · Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it · Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
+          <t>STEP 2 — which family owns the variation  ·  Key:
+• Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared
+• Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64). It is what a sum of squares is divided by to get a mean square, and it is why a family measured across two levels can never be pinned down as tightly as one measured across ten
+• Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it
+• Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
         </is>
       </c>
       <c r="B61" s="7" t="n"/>

--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -112,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -136,6 +141,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,7 +486,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -500,7 +508,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>20</row>
       <rowOff>0</rowOff>
@@ -985,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -996,6 +1004,15 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1370,7 +1387,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Manchester</t>
@@ -1394,6 +1411,12 @@
       <c r="E21" s="14" t="n">
         <v>398</v>
       </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Shares of VARIANCE, so they add to 100% while the standard deviations behind them do not. Attack the tallest bar. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family nested inside it, which is a sampling result and not a finding.
+SO:  Aim the project at the tallest bar. If it is the within-agent bar, no amount of team-level management will touch it; if it is between teams, the individuals are not the problem and coaching them is wasted effort.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -1752,7 +1775,14 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
+    <row r="37" ht="77" customHeight="1">
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  One point per agent, grouped by team and site, so the eye can see which level the spread lives at. Bars level within a team but stepped between teams point at supervision or routing; scatter inside a team points at the individuals. The axis starts at zero because seconds do.
+SO:  Where the spread is inside teams rather than between them, work on the method every agent follows, not on the outliers. Ranking agents off this chart re-labels normal variation as performance and costs you the people at the bottom.</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
@@ -1812,19 +1842,19 @@
           <t>R. Okonjo · Billing A</t>
         </is>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="16">
         <f>AVERAGE(E12:E13)</f>
         <v/>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="17">
         <f>COUNT(E12:E13)</f>
         <v/>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="18">
         <f>C40-C52</f>
         <v/>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="18">
         <f>E12-E13</f>
         <v/>
       </c>
@@ -1840,19 +1870,19 @@
           <t>P. Adeyemi · Billing A</t>
         </is>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="16">
         <f>AVERAGE(E14:E15)</f>
         <v/>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="17">
         <f>COUNT(E14:E15)</f>
         <v/>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="18">
         <f>C41-C52</f>
         <v/>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="18">
         <f>E14-E15</f>
         <v/>
       </c>
@@ -1868,19 +1898,19 @@
           <t>S. Novak · Billing A</t>
         </is>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="16">
         <f>AVERAGE(E16:E17)</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="17">
         <f>COUNT(E16:E17)</f>
         <v/>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="18">
         <f>C42-C52</f>
         <v/>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="18">
         <f>E16-E17</f>
         <v/>
       </c>
@@ -1896,19 +1926,19 @@
           <t>T. Iqbal · Billing B</t>
         </is>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="16">
         <f>AVERAGE(E18:E19)</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <f>COUNT(E18:E19)</f>
         <v/>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="18">
         <f>C43-C53</f>
         <v/>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="18">
         <f>E18-E19</f>
         <v/>
       </c>
@@ -1924,19 +1954,19 @@
           <t>M. Chen · Billing B</t>
         </is>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="16">
         <f>AVERAGE(E20:E21)</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="17">
         <f>COUNT(E20:E21)</f>
         <v/>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="18">
         <f>C44-C53</f>
         <v/>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="18">
         <f>E20-E21</f>
         <v/>
       </c>
@@ -1952,19 +1982,19 @@
           <t>L. Haddad · Billing B</t>
         </is>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="16">
         <f>AVERAGE(E22:E23)</f>
         <v/>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <f>COUNT(E22:E23)</f>
         <v/>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="18">
         <f>C45-C53</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="18">
         <f>E22-E23</f>
         <v/>
       </c>
@@ -1980,19 +2010,19 @@
           <t>J. Barros · Billing C</t>
         </is>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="16">
         <f>AVERAGE(E24:E25)</f>
         <v/>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <f>COUNT(E24:E25)</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <f>C46-C54</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="18">
         <f>E24-E25</f>
         <v/>
       </c>
@@ -2008,19 +2038,19 @@
           <t>D. Wexler · Billing C</t>
         </is>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="16">
         <f>AVERAGE(E26:E27)</f>
         <v/>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <f>COUNT(E26:E27)</f>
         <v/>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="18">
         <f>C47-C54</f>
         <v/>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="18">
         <f>E26-E27</f>
         <v/>
       </c>
@@ -2036,19 +2066,19 @@
           <t>A. Ferreira · Billing C</t>
         </is>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="16">
         <f>AVERAGE(E28:E29)</f>
         <v/>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="17">
         <f>COUNT(E28:E29)</f>
         <v/>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="18">
         <f>C48-C54</f>
         <v/>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="18">
         <f>E28-E29</f>
         <v/>
       </c>
@@ -2064,19 +2094,19 @@
           <t>K. Nowak · Billing D</t>
         </is>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="16">
         <f>AVERAGE(E30:E31)</f>
         <v/>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <f>COUNT(E30:E31)</f>
         <v/>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="18">
         <f>C49-C55</f>
         <v/>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="18">
         <f>E30-E31</f>
         <v/>
       </c>
@@ -2092,19 +2122,19 @@
           <t>E. Duarte · Billing D</t>
         </is>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="16">
         <f>AVERAGE(E32:E33)</f>
         <v/>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="17">
         <f>COUNT(E32:E33)</f>
         <v/>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="18">
         <f>C50-C55</f>
         <v/>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="18">
         <f>E32-E33</f>
         <v/>
       </c>
@@ -2120,19 +2150,19 @@
           <t>N. Osei · Billing D</t>
         </is>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="16">
         <f>AVERAGE(E34:E35)</f>
         <v/>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <f>COUNT(E34:E35)</f>
         <v/>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="18">
         <f>C51-C55</f>
         <v/>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="18">
         <f>E34-E35</f>
         <v/>
       </c>
@@ -2148,15 +2178,15 @@
           <t>Billing A · Manchester</t>
         </is>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="16">
         <f>AVERAGE(E12:E17)</f>
         <v/>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <f>COUNT(E12:E17)</f>
         <v/>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="18">
         <f>C52-C56</f>
         <v/>
       </c>
@@ -2172,15 +2202,15 @@
           <t>Billing B · Manchester</t>
         </is>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="16">
         <f>AVERAGE(E18:E23)</f>
         <v/>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <f>COUNT(E18:E23)</f>
         <v/>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="18">
         <f>C53-C56</f>
         <v/>
       </c>
@@ -2196,15 +2226,15 @@
           <t>Billing C · Kraków</t>
         </is>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="16">
         <f>AVERAGE(E24:E29)</f>
         <v/>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="17">
         <f>COUNT(E24:E29)</f>
         <v/>
       </c>
-      <c r="E54" s="17">
+      <c r="E54" s="18">
         <f>C54-C57</f>
         <v/>
       </c>
@@ -2220,15 +2250,15 @@
           <t>Billing D · Kraków</t>
         </is>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="16">
         <f>AVERAGE(E30:E35)</f>
         <v/>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="17">
         <f>COUNT(E30:E35)</f>
         <v/>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="18">
         <f>C55-C57</f>
         <v/>
       </c>
@@ -2244,15 +2274,15 @@
           <t>Manchester</t>
         </is>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="16">
         <f>AVERAGE(E12:E23)</f>
         <v/>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="17">
         <f>COUNT(E12:E23)</f>
         <v/>
       </c>
-      <c r="E56" s="17">
+      <c r="E56" s="18">
         <f>C56-C58</f>
         <v/>
       </c>
@@ -2268,15 +2298,15 @@
           <t>Kraków</t>
         </is>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="16">
         <f>AVERAGE(E24:E35)</f>
         <v/>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="17">
         <f>COUNT(E24:E35)</f>
         <v/>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="18">
         <f>C57-C58</f>
         <v/>
       </c>
@@ -2292,11 +2322,11 @@
           <t>Grand mean</t>
         </is>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="16">
         <f>AVERAGE(E12:E35)</f>
         <v/>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="17">
         <f>COUNT(E12:E35)</f>
         <v/>
       </c>
@@ -2310,7 +2340,7 @@
     </row>
     <row r="60"/>
     <row r="61" ht="204" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>STEP 2 — which family owns the variation  ·  Key:
 • Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared
@@ -2371,22 +2401,22 @@
           <t>Between sites</t>
         </is>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="20">
         <f>12*SUMSQ(E56:E57)</f>
         <v/>
       </c>
-      <c r="C63" s="16" t="n">
+      <c r="C63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="20">
         <f>B63/C63</f>
         <v/>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="20">
         <f>MAX(0,(D63-D64)/12)</f>
         <v/>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="21">
         <f>IFERROR(E63/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2402,22 +2432,22 @@
           <t>Between teams, within a site</t>
         </is>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="20">
         <f>6*SUMSQ(E52:E55)</f>
         <v/>
       </c>
-      <c r="C64" s="16" t="n">
+      <c r="C64" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="20">
         <f>B64/C64</f>
         <v/>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="20">
         <f>MAX(0,(D64-D65)/6)</f>
         <v/>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="21">
         <f>IFERROR(E64/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2433,22 +2463,22 @@
           <t>Between agents, within a team</t>
         </is>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="20">
         <f>2*SUMSQ(E40:E51)</f>
         <v/>
       </c>
-      <c r="C65" s="16" t="n">
+      <c r="C65" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="20">
         <f>B65/C65</f>
         <v/>
       </c>
-      <c r="E65" s="19">
+      <c r="E65" s="20">
         <f>MAX(0,(D65-D66)/2)</f>
         <v/>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="21">
         <f>IFERROR(E65/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2464,22 +2494,22 @@
           <t>Within one agent, contact to contact</t>
         </is>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="20">
         <f>SUMSQ(F40:F51)/2</f>
         <v/>
       </c>
-      <c r="C66" s="16" t="n">
+      <c r="C66" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="20">
         <f>B66/C66</f>
         <v/>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="20">
         <f>D66</f>
         <v/>
       </c>
-      <c r="F66" s="20">
+      <c r="F66" s="21">
         <f>IFERROR(E66/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
@@ -2495,14 +2525,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f>DEVSQ(E12:E35)</f>
         <v/>
       </c>
-      <c r="C67" s="16" t="n">
+      <c r="C67" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f>IFERROR(SUM(F63:F66),"")</f>
         <v/>
       </c>
@@ -2547,7 +2577,7 @@
           <t>Look here first</t>
         </is>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="22">
         <f>IFERROR(INDEX($A$63:$A$66,MATCH(MAX($F$63:$F$66),$F$63:$F$66,0)),"")</f>
         <v/>
       </c>
@@ -2563,7 +2593,7 @@
           <t>Biggest gap between two agents (s)</t>
         </is>
       </c>
-      <c r="B73" s="15">
+      <c r="B73" s="16">
         <f>IFERROR(MAX(C40:C51)-MIN(C40:C51),"")</f>
         <v/>
       </c>
@@ -2579,7 +2609,7 @@
           <t>Is that gap worth chasing?</t>
         </is>
       </c>
-      <c r="B74" s="21">
+      <c r="B74" s="22">
         <f>IF(B73="","",IF(B73&gt;=$B$8,"YES — larger than the difference you said would matter","NO — smaller than the difference you said would matter"))</f>
         <v/>
       </c>
@@ -2595,7 +2625,7 @@
           <t>Contacts per agent needed to halve the noise</t>
         </is>
       </c>
-      <c r="B75" s="15">
+      <c r="B75" s="16">
         <f>IFERROR(ROUNDUP(4*E66/(($B$8/2)^2),0),"")</f>
         <v/>
       </c>
@@ -2606,7 +2636,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="A59:H59"/>
     <mergeCell ref="C75:H75"/>
     <mergeCell ref="G67:H67"/>
@@ -2617,6 +2647,7 @@
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="G66:H66"/>
     <mergeCell ref="C7:H7"/>
+    <mergeCell ref="J21:R21"/>
     <mergeCell ref="C72:H72"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
@@ -2629,6 +2660,7 @@
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="C74:H74"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="J37:R37"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="C73:H73"/>
   </mergeCells>

--- a/templates/31-multi-vari.xlsx
+++ b/templates/31-multi-vari.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,10 @@
       <i val="1"/>
       <color rgb="FF4B5563"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -117,12 +121,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,9 +151,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -820,11 +827,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="108" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -956,11 +969,41 @@
     </row>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64). It is what a sum of squares is divided by to get a mean square, and it is why a family measured across two levels can never be pinned down as tightly as one measured across ten</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
+        </is>
+      </c>
+    </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
@@ -976,10 +1019,15 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B15"/>
+  <mergeCells count="8">
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B13"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1016,21 +1064,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Multi-vari study — which family of variation owns the problem</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Before you improve anything, find out where the variation lives: between sites, between teams, between agents, or inside one agent from one contact to the next. Improving the wrong family is the most expensive mistake in the Measure phase. The green block is a worked example — replace it with your own extract.</t>
         </is>
@@ -1038,80 +1086,80 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>THE QUESTION — what you are partitioning, and how the contacts were drawn</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>What you are measuring</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Handle time in seconds, CRM open to CRM close</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>One measurement, with its start and stop written down. A multi-vari study on 'productivity' partitions an opinion.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>The families you sampled, outer to inner</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Site → team → agent → contact</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Each family has to sit INSIDE the one before it. Agents belong to one team, teams to one site. If a family cuts across the others — shift, say, or contact type — it is not nested and this sheet will mis-attribute it.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>How the contacts were drawn</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Two consecutive contacts per agent, same week</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Consecutive and close together on purpose: the innermost family is meant to capture contact-to-contact variation, not the drift between March and June.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Smallest difference worth chasing (seconds)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The gap you would actually change something for. Set it before you look at the answer, or you will set it to whatever the answer turned out to be.</t>
         </is>
@@ -1119,299 +1167,299 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>THE DATA — one row per contact, nested: site, then team, then agent</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Contact ref</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Handle time (seconds)</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>R. Okonjo</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>BA-3001</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="16" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>R. Okonjo</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>BA-3002</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="16" t="n">
         <v>377</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>P. Adeyemi</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>BA-3003</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="16" t="n">
         <v>478</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>P. Adeyemi</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>BA-3004</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="16" t="n">
         <v>415</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>S. Novak</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>BA-3005</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="16" t="n">
         <v>356</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Billing A</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>S. Novak</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>BA-3006</t>
         </is>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="16" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>T. Iqbal</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>BA-3007</t>
         </is>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="16" t="n">
         <v>527</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>T. Iqbal</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>BA-3008</t>
         </is>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="16" t="n">
         <v>462</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>M. Chen</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>BA-3009</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="16" t="n">
         <v>341</v>
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>M. Chen</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>BA-3010</t>
         </is>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="16" t="n">
         <v>398</v>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Shares of VARIANCE, so they add to 100% while the standard deviations behind them do not. Attack the tallest bar. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family nested inside it, which is a sampling result and not a finding.
 SO:  Aim the project at the tallest bar. If it is the within-agent bar, no amount of team-level management will touch it; if it is between teams, the individuals are not the problem and coaching them is wasted effort.</t>
@@ -1419,364 +1467,364 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>L. Haddad</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>BA-3011</t>
         </is>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="16" t="n">
         <v>401</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Manchester</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Billing B</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>L. Haddad</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>BA-3012</t>
         </is>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="16" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>J. Barros</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>BA-3013</t>
         </is>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="16" t="n">
         <v>438</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>J. Barros</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>BA-3014</t>
         </is>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="16" t="n">
         <v>375</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>D. Wexler</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>BA-3015</t>
         </is>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="16" t="n">
         <v>552</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>D. Wexler</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>BA-3016</t>
         </is>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="16" t="n">
         <v>487</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>A. Ferreira</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>BA-3017</t>
         </is>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="16" t="n">
         <v>329</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Billing C</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>A. Ferreira</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>BA-3018</t>
         </is>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="16" t="n">
         <v>388</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>K. Nowak</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>BA-3019</t>
         </is>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="16" t="n">
         <v>495</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>K. Nowak</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>BA-3020</t>
         </is>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="16" t="n">
         <v>433</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>E. Duarte</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>BA-3021</t>
         </is>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="16" t="n">
         <v>368</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>E. Duarte</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>BA-3022</t>
         </is>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="16" t="n">
         <v>424</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>N. Osei</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>BA-3023</t>
         </is>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="16" t="n">
         <v>571</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Kraków</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Billing D</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>N. Osei</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>BA-3024</t>
         </is>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E35" s="16" t="n">
         <v>505</v>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Twenty-four contacts: 2 sites × 2 teams × 3 agents × 2 contacts each. Keep it balanced. The arithmetic below splits the variation using the mean square of each family, and a mean square only means what it is supposed to when every cell holds the same number of contacts. Add an agent and you add two rows, not one; drop a contact and the partition below is no longer a partition.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="77" customHeight="1">
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  One point per agent, grouped by team and site, so the eye can see which level the spread lives at. Bars level within a team but stepped between teams point at supervision or routing; scatter inside a team points at the individuals. The axis starts at zero because seconds do.
 SO:  Where the spread is inside teams rather than between them, work on the method every agent follows, not on the outliers. Ranking agents off this chart re-labels normal variation as performance and costs you the people at the bottom.</t>
@@ -1784,52 +1832,52 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>STEP 1 — the averages, from the bottom up</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Mean handle time (s)</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Contacts behind it</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Gap to its parent (s)</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Spread inside (s)</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1842,19 +1890,19 @@
           <t>R. Okonjo · Billing A</t>
         </is>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="17">
         <f>AVERAGE(E12:E13)</f>
         <v/>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="18">
         <f>COUNT(E12:E13)</f>
         <v/>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="19">
         <f>C40-C52</f>
         <v/>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="19">
         <f>E12-E13</f>
         <v/>
       </c>
@@ -1870,19 +1918,19 @@
           <t>P. Adeyemi · Billing A</t>
         </is>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <f>AVERAGE(E14:E15)</f>
         <v/>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="18">
         <f>COUNT(E14:E15)</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="19">
         <f>C41-C52</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="19">
         <f>E14-E15</f>
         <v/>
       </c>
@@ -1898,19 +1946,19 @@
           <t>S. Novak · Billing A</t>
         </is>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <f>AVERAGE(E16:E17)</f>
         <v/>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="18">
         <f>COUNT(E16:E17)</f>
         <v/>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="19">
         <f>C42-C52</f>
         <v/>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <f>E16-E17</f>
         <v/>
       </c>
@@ -1926,19 +1974,19 @@
           <t>T. Iqbal · Billing B</t>
         </is>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="17">
         <f>AVERAGE(E18:E19)</f>
         <v/>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="18">
         <f>COUNT(E18:E19)</f>
         <v/>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="19">
         <f>C43-C53</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <f>E18-E19</f>
         <v/>
       </c>
@@ -1954,19 +2002,19 @@
           <t>M. Chen · Billing B</t>
         </is>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="17">
         <f>AVERAGE(E20:E21)</f>
         <v/>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="18">
         <f>COUNT(E20:E21)</f>
         <v/>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="19">
         <f>C44-C53</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <f>E20-E21</f>
         <v/>
       </c>
@@ -1982,19 +2030,19 @@
           <t>L. Haddad · Billing B</t>
         </is>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="17">
         <f>AVERAGE(E22:E23)</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="18">
         <f>COUNT(E22:E23)</f>
         <v/>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="19">
         <f>C45-C53</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <f>E22-E23</f>
         <v/>
       </c>
@@ -2010,19 +2058,19 @@
           <t>J. Barros · Billing C</t>
         </is>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="17">
         <f>AVERAGE(E24:E25)</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="18">
         <f>COUNT(E24:E25)</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="19">
         <f>C46-C54</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="19">
         <f>E24-E25</f>
         <v/>
       </c>
@@ -2038,19 +2086,19 @@
           <t>D. Wexler · Billing C</t>
         </is>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="17">
         <f>AVERAGE(E26:E27)</f>
         <v/>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="18">
         <f>COUNT(E26:E27)</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="19">
         <f>C47-C54</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="19">
         <f>E26-E27</f>
         <v/>
       </c>
@@ -2066,19 +2114,19 @@
           <t>A. Ferreira · Billing C</t>
         </is>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="17">
         <f>AVERAGE(E28:E29)</f>
         <v/>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="18">
         <f>COUNT(E28:E29)</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="19">
         <f>C48-C54</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="19">
         <f>E28-E29</f>
         <v/>
       </c>
@@ -2094,19 +2142,19 @@
           <t>K. Nowak · Billing D</t>
         </is>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="17">
         <f>AVERAGE(E30:E31)</f>
         <v/>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="18">
         <f>COUNT(E30:E31)</f>
         <v/>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="19">
         <f>C49-C55</f>
         <v/>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="19">
         <f>E30-E31</f>
         <v/>
       </c>
@@ -2122,19 +2170,19 @@
           <t>E. Duarte · Billing D</t>
         </is>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="17">
         <f>AVERAGE(E32:E33)</f>
         <v/>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="18">
         <f>COUNT(E32:E33)</f>
         <v/>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="19">
         <f>C50-C55</f>
         <v/>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="19">
         <f>E32-E33</f>
         <v/>
       </c>
@@ -2150,19 +2198,19 @@
           <t>N. Osei · Billing D</t>
         </is>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="17">
         <f>AVERAGE(E34:E35)</f>
         <v/>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="18">
         <f>COUNT(E34:E35)</f>
         <v/>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="19">
         <f>C51-C55</f>
         <v/>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="19">
         <f>E34-E35</f>
         <v/>
       </c>
@@ -2178,15 +2226,15 @@
           <t>Billing A · Manchester</t>
         </is>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="17">
         <f>AVERAGE(E12:E17)</f>
         <v/>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="18">
         <f>COUNT(E12:E17)</f>
         <v/>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="19">
         <f>C52-C56</f>
         <v/>
       </c>
@@ -2202,15 +2250,15 @@
           <t>Billing B · Manchester</t>
         </is>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="17">
         <f>AVERAGE(E18:E23)</f>
         <v/>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="18">
         <f>COUNT(E18:E23)</f>
         <v/>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="19">
         <f>C53-C56</f>
         <v/>
       </c>
@@ -2226,15 +2274,15 @@
           <t>Billing C · Kraków</t>
         </is>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="17">
         <f>AVERAGE(E24:E29)</f>
         <v/>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="18">
         <f>COUNT(E24:E29)</f>
         <v/>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="19">
         <f>C54-C57</f>
         <v/>
       </c>
@@ -2250,15 +2298,15 @@
           <t>Billing D · Kraków</t>
         </is>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="17">
         <f>AVERAGE(E30:E35)</f>
         <v/>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="18">
         <f>COUNT(E30:E35)</f>
         <v/>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="19">
         <f>C55-C57</f>
         <v/>
       </c>
@@ -2274,15 +2322,15 @@
           <t>Manchester</t>
         </is>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="17">
         <f>AVERAGE(E12:E23)</f>
         <v/>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="18">
         <f>COUNT(E12:E23)</f>
         <v/>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="19">
         <f>C56-C58</f>
         <v/>
       </c>
@@ -2298,259 +2346,259 @@
           <t>Kraków</t>
         </is>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="17">
         <f>AVERAGE(E24:E35)</f>
         <v/>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="18">
         <f>COUNT(E24:E35)</f>
         <v/>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="19">
         <f>C57-C58</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>All contacts</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Grand mean</t>
         </is>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="17">
         <f>AVERAGE(E12:E35)</f>
         <v/>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="18">
         <f>COUNT(E12:E35)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>Read the GAP column, not the means. Every gap is measured against the level that contains it — an agent against their own team, a team against its own site — so the four families never claim the same second twice. SPREAD INSIDE is the difference between one agent's two contacts, and it is the only column here that owes nothing to who or where they are.</t>
         </is>
       </c>
     </row>
     <row r="60"/>
-    <row r="61" ht="204" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="61" ht="84" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>STEP 2 — which family owns the variation  ·  Key:
-• Sum of squares = total squared distance from the mean, before it is divided by anything. Two of them can never be compared directly, because each carries a different number of degrees of freedom: parts contribute 644.15 over 9 df and the repeat readings 6.53 over 60 (B47, B50). Divide each by its own df and you get the mean squares, 71.57 against 0.109, which may be compared
-• Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64). It is what a sum of squares is divided by to get a mean square, and it is why a family measured across two levels can never be pinned down as tightly as one measured across ten
-• Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes. Repeatability is 0.109 and reproducibility 0.589 (B56, B57) — a ratio of 5.4 on the squared scale, which is 2.3 once you take square roots and get back to minutes, 0.33 against 0.77. Quote the minutes to anyone who has to act on it
-• Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent. The shares are of VARIANCE, so they add to 100% while the standard deviations they come from do not. A family clamped to zero has not been shown to be identical — only that this sample cannot separate it from the family inside it</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
+• Sum of squares = total squared distance from the mean, before it is divided by anything.
+• Degrees of freedom = the number of independent comparisons that family supports: 1 between two sites, 2 between the three teams inside them (C63, C64).
+• Variance component = that source's share of the variation as a VARIANCE, in minutes squared, not minutes.
+• Share of total = that family's variance as a percentage of the total variance, which is how a multi-vari study apportions the spread between sites, teams, agents and the noise within one agent.</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>Sum of squares</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>Mean square</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>Variance component</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="F62" s="14" t="inlineStr">
         <is>
           <t>Share of total</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>What this family means</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr"/>
+      <c r="H62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Between sites</t>
         </is>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="21">
         <f>12*SUMSQ(E56:E57)</f>
         <v/>
       </c>
-      <c r="C63" s="17" t="n">
+      <c r="C63" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="21">
         <f>B63/C63</f>
         <v/>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="21">
         <f>MAX(0,(D63-D64)/12)</f>
         <v/>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="22">
         <f>IFERROR(E63/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>Manchester against Kraków, once the teams and agents inside them are accounted for. A big share here means the two sites are running different processes.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Between teams, within a site</t>
         </is>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="21">
         <f>6*SUMSQ(E52:E55)</f>
         <v/>
       </c>
-      <c r="C64" s="17" t="n">
+      <c r="C64" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="21">
         <f>B64/C64</f>
         <v/>
       </c>
-      <c r="E64" s="20">
+      <c r="E64" s="21">
         <f>MAX(0,(D64-D65)/6)</f>
         <v/>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="22">
         <f>IFERROR(E64/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>One billing team against another in the same building — different team leader, different coaching, same everything else.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Between agents, within a team</t>
         </is>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="21">
         <f>2*SUMSQ(E40:E51)</f>
         <v/>
       </c>
-      <c r="C65" s="17" t="n">
+      <c r="C65" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="21">
         <f>B65/C65</f>
         <v/>
       </c>
-      <c r="E65" s="20">
+      <c r="E65" s="21">
         <f>MAX(0,(D65-D66)/2)</f>
         <v/>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="22">
         <f>IFERROR(E65/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>One agent against their own team-mates. A big share here is a training, tooling or method problem, and it is the family a site-level project cannot touch.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Within one agent, contact to contact</t>
         </is>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="21">
         <f>SUMSQ(F40:F51)/2</f>
         <v/>
       </c>
-      <c r="C66" s="17" t="n">
+      <c r="C66" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="21">
         <f>B66/C66</f>
         <v/>
       </c>
-      <c r="E66" s="20">
+      <c r="E66" s="21">
         <f>D66</f>
         <v/>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="22">
         <f>IFERROR(E66/SUM($E$63:$E$66),"")</f>
         <v/>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>The same agent, two contacts, one week. Whatever is left after everything you can name — contact mix, system waits, luck. It sets the floor on what any of the families above can be measured against.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="21">
         <f>DEVSQ(E12:E35)</f>
         <v/>
       </c>
-      <c r="C67" s="17" t="n">
+      <c r="C67" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="22">
         <f>IFERROR(SUM(F63:F66),"")</f>
         <v/>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>The four sums of squares add up to this one exactly. If they ever do not, the design has stopped being balanced.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>A VARIANCE COMPONENT can come out negative, and one has here: the teams component is showing zero because the arithmetic produced a number below zero and there is no such thing as negative variance. It does not mean the teams are identical. It means this sample cannot tell teams apart from the agents sitting inside them — the agent-to-agent spread is wide enough to swallow any team effect. Report it as zero, say why, and if the team question matters, go back with more agents per team rather than more contacts per agent.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>SUM OF SQUARES says how much of the raw spread each family accounts for; the VARIANCE COMPONENT is what is left after removing the variation the families underneath already explain, and it is the one to quote. They rank differently on purpose. Share of total is computed on the components.</t>
         </is>
@@ -2558,78 +2606,78 @@
     </row>
     <row r="70"/>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>STEP 3 — what it tells you to do next</t>
         </is>
       </c>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n"/>
+      <c r="H71" s="9" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>Look here first</t>
         </is>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="23">
         <f>IFERROR(INDEX($A$63:$A$66,MATCH(MAX($F$63:$F$66),$F$63:$F$66,0)),"")</f>
         <v/>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>The family holding the largest share. Scope your project to this family — an improvement aimed anywhere else is competing with variation it cannot reach.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>Biggest gap between two agents (s)</t>
         </is>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="17">
         <f>IFERROR(MAX(C40:C51)-MIN(C40:C51),"")</f>
         <v/>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Fastest agent against slowest, in seconds of handle time. This is the number to take to the process owner, because it is one they can picture.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Is that gap worth chasing?</t>
         </is>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <f>IF(B73="","",IF(B73&gt;=$B$8,"YES — larger than the difference you said would matter","NO — smaller than the difference you said would matter"))</f>
         <v/>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Measured against the threshold you set at the top, before you saw the data.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Contacts per agent needed to halve the noise</t>
         </is>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="17">
         <f>IFERROR(ROUNDUP(4*E66/(($B$8/2)^2),0),"")</f>
         <v/>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>If the answer above is too close to call, this is roughly how many contacts per agent the next study needs to resolve half your threshold. It grows with the square, which is why precision gets expensive quickly.</t>
         </is>
